--- a/Result/profitability/6236.xlsx
+++ b/Result/profitability/6236.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-1.22</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.14875</v>
+        <v>-0.1375</v>
       </c>
       <c r="N2" t="n">
-        <v>75.01375</v>
+        <v>76.07124999999999</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-1.04</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.2675</v>
+        <v>-0.2725</v>
       </c>
       <c r="N3" t="n">
-        <v>63.69624999999999</v>
+        <v>63.3025</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.76</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.3675</v>
+        <v>-0.37625</v>
       </c>
       <c r="N4" t="n">
-        <v>56.55375</v>
+        <v>56.5</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
         <v>-0.40375</v>
       </c>
       <c r="N5" t="n">
-        <v>49.62875</v>
+        <v>49.9575</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>-0.67</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.4875</v>
+        <v>-0.485</v>
       </c>
       <c r="N6" t="n">
-        <v>40.79000000000001</v>
+        <v>40.99625</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.25</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.51625</v>
+        <v>-0.52</v>
       </c>
       <c r="N7" t="n">
-        <v>39.08875</v>
+        <v>38.63625</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>-0.54</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.5874999999999999</v>
+        <v>-0.5875</v>
       </c>
       <c r="N8" t="n">
-        <v>33.26625</v>
+        <v>33.325</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
         <v>-0.45</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.5599999999999999</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="N10" t="n">
         <v>25.09625</v>
@@ -9828,6 +9828,129 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6236</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>8</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1</v>
+      </c>
+      <c r="E75" t="n">
+        <v>7</v>
+      </c>
+      <c r="F75" t="n">
+        <v>83.42</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-9.72%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>1</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.003750000000000014</v>
+      </c>
+      <c r="N75" t="n">
+        <v>82.66875</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0</v>
+      </c>
+      <c r="X75" t="inlineStr"/>
+      <c r="Y75" t="n">
+        <v>0.4699999999999989</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.005666063893911888</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB75" t="inlineStr"/>
+      <c r="AC75" t="n">
+        <v>2.629999999999995</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.0325535338531997</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
